--- a/data/test_files/challenge/challenge_sparse_rows.xlsx
+++ b/data/test_files/challenge/challenge_sparse_rows.xlsx
@@ -4,15 +4,16 @@
   <sheets>
     <sheet name="Leads" sheetId="1" r:id="rId3"/>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
-    <sheet name="Tab 02" sheetId="3" r:id="rId2"/>
-    <sheet name="Tab 04" sheetId="4" r:id="rId4"/>
-    <sheet name="Tab 05" sheetId="5" r:id="rId5"/>
-    <sheet name="Tab 06" sheetId="6" r:id="rId6"/>
-    <sheet name="Tab 07" sheetId="7" r:id="rId7"/>
-    <sheet name="Tab 08" sheetId="8" r:id="rId8"/>
-    <sheet name="Tab 09" sheetId="9" r:id="rId9"/>
-    <sheet name="Tab 10" sheetId="10" r:id="rId10"/>
-    <sheet name="Tab 11" sheetId="11" r:id="rId11"/>
+    <sheet name="Gaps" sheetId="3" r:id="rId12"/>
+    <sheet name="Tab 02" sheetId="4" r:id="rId2"/>
+    <sheet name="Tab 04" sheetId="5" r:id="rId4"/>
+    <sheet name="Tab 05" sheetId="6" r:id="rId5"/>
+    <sheet name="Tab 06" sheetId="7" r:id="rId6"/>
+    <sheet name="Tab 07" sheetId="8" r:id="rId7"/>
+    <sheet name="Tab 08" sheetId="9" r:id="rId8"/>
+    <sheet name="Tab 09" sheetId="10" r:id="rId9"/>
+    <sheet name="Tab 10" sheetId="11" r:id="rId10"/>
+    <sheet name="Tab 11" sheetId="12" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -82,86 +83,145 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Sheet part</t>
-        </is>
-      </c>
-      <c r="B1">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>First name</t>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Row</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>r5</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>r6</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>r400</t>
+        </is>
+      </c>
+      <c r="B400">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sheet part</t>
+        </is>
+      </c>
+      <c r="B1">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>First name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>

--- a/data/test_files/challenge/challenge_sparse_rows.xlsx
+++ b/data/test_files/challenge/challenge_sparse_rows.xlsx
@@ -222,22 +222,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adapt</t>
+          <t>ExampleCo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adaptagency.com</t>
+          <t>example-co.example</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kresten Finsen Wiinblad</t>
+          <t>Sam Placeholder</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -247,7 +247,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LinkedIn outreach, 3 July 2026</t>
+          <t>Intro call, 3 July 2026</t>
         </is>
       </c>
     </row>
